--- a/РАБОЧИЙ СТОЛ/расчеты ПОКОМ КИ/дв 11,08,26 лгрсч пок ки.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты ПОКОМ КИ/дв 11,08,26 лгрсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EC977D2-2B77-4B2E-AC35-A983EA5219FD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE29950-5291-4BB3-BFDB-AB14BB9C0768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,15 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AH$136</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -632,7 +624,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -673,6 +665,18 @@
         <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -709,7 +713,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -726,6 +730,8 @@
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1283,7 +1289,7 @@
       <c r="O4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="11" t="s">
+      <c r="P4" s="16" t="s">
         <v>23</v>
       </c>
       <c r="Q4" s="11" t="s">
@@ -1387,7 +1393,7 @@
       </c>
       <c r="Q5" s="3">
         <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>1000</v>
       </c>
       <c r="R5" s="3">
         <f t="shared" si="0"/>
@@ -4291,8 +4297,8 @@
       <c r="P32" s="11">
         <v>-1008</v>
       </c>
-      <c r="Q32" s="11">
-        <v>1050</v>
+      <c r="Q32" s="16">
+        <v>0</v>
       </c>
       <c r="R32" s="11"/>
       <c r="S32" s="11">
@@ -4304,11 +4310,11 @@
       </c>
       <c r="U32" s="11">
         <f t="shared" si="4"/>
-        <v>-9281.9782214156075</v>
+        <v>-4517.912885662432</v>
       </c>
       <c r="V32" s="11">
         <f t="shared" si="5"/>
-        <v>-4744.7731397459165</v>
+        <v>19.292196007259314</v>
       </c>
       <c r="W32" s="11">
         <v>466.95479999999998</v>
@@ -10670,7 +10676,9 @@
       <c r="P91" s="11">
         <v>0</v>
       </c>
-      <c r="Q91" s="11"/>
+      <c r="Q91" s="17">
+        <v>1000</v>
+      </c>
       <c r="R91" s="11">
         <v>900</v>
       </c>
@@ -10681,11 +10689,11 @@
       <c r="T91" s="4"/>
       <c r="U91" s="11">
         <f t="shared" si="16"/>
-        <v>11.079506009405058</v>
+        <v>13.400366881686692</v>
       </c>
       <c r="V91" s="11">
         <f t="shared" si="17"/>
-        <v>11.079506009405058</v>
+        <v>13.400366881686692</v>
       </c>
       <c r="W91" s="11">
         <v>398.44540000000001</v>
@@ -15208,7 +15216,7 @@
         <v>79</v>
       </c>
       <c r="L134" s="11">
-        <f t="shared" ref="L134:L165" si="24">E134-K134</f>
+        <f t="shared" ref="L134:L136" si="24">E134-K134</f>
         <v>-12</v>
       </c>
       <c r="M134" s="11"/>
@@ -15230,7 +15238,7 @@
         <v>80.100000000000023</v>
       </c>
       <c r="U134" s="11">
-        <f t="shared" ref="U134:U165" si="25">(F134+O134+P134+Q134+R134+T134)/S134</f>
+        <f t="shared" ref="U134:U136" si="25">(F134+O134+P134+Q134+R134+T134)/S134</f>
         <v>11</v>
       </c>
       <c r="V134" s="11">
